--- a/data/demo/Linkbits-Traffic-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/Linkbits-Traffic-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="257">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,718 +23,730 @@
     <t>Audífonos Inalámbricos para la Cabeza, Recargables y Multifuncionales - Conectan a Varios Dispositivos, soportan Radio FM, Tarjeta TF y AUX - 4 Horas de Reproducción Musical - Ideal para Trabajo Cotidiano, Juegos y Estudio</t>
   </si>
   <si>
-    <t>85915</t>
-  </si>
-  <si>
-    <t>67034</t>
-  </si>
-  <si>
-    <t>870</t>
+    <t>131984</t>
+  </si>
+  <si>
+    <t>101563</t>
+  </si>
+  <si>
+    <t>1375</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>1.04%</t>
+  </si>
+  <si>
+    <t>602978090117530</t>
+  </si>
+  <si>
+    <t>Bocina inalámbrica de la marca LINK BITS. Tiene un altavoz grande de 8 pulgadas, un sonido estéreo, una interfaz USB. Tiene una batería recargable interna de 1200 mAh. Cuenta con funciones de control de altavoz y microfono. Tiene luces LED. Apoya tarjetas TF, la recepción de radio FM y la interconexión inalámbrica TWS (True Wireless Stereo). Es una bocina adecuada para fiestas en casa, karaoke y uso al aire libre.</t>
+  </si>
+  <si>
+    <t>9165</t>
+  </si>
+  <si>
+    <t>6931</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>2.16%</t>
+  </si>
+  <si>
+    <t>604444133541993</t>
+  </si>
+  <si>
+    <t>Soporte Articulado de Pared para TV LCD LED Smart de 14 a 55 Pulgadas, Brazo Telescópico 3 Brazos Extensible y Retráctil, Giro Horizontal ±90°, Inclinación ±15°, Carga Hasta 25kg, Compatible VESA 75x75 hasta 400x400, Para Pared de Ladrillo, Madera y Hormigón</t>
+  </si>
+  <si>
+    <t>9756</t>
+  </si>
+  <si>
+    <t>8405</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>0.74%</t>
+  </si>
+  <si>
+    <t>608113864355784</t>
+  </si>
+  <si>
+    <t>Audífonos diadema over-ear Bluetooth 5.4 con micrófono HD y baja latencia, plegables ergonómicos para estudiar, ver series y jugar en celular, laptop y consola, conexión estable sin cortes</t>
+  </si>
+  <si>
+    <t>15710</t>
+  </si>
+  <si>
+    <t>11157</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>2.64%</t>
+  </si>
+  <si>
+    <t>604835730556993</t>
+  </si>
+  <si>
+    <t>Bocina portátil Inalámbrico, de 3 pulgadas, tamaño de bolsillo, 170 g, con asa, compatible con TF, USB y Micro SD, con radio FM y función TWS (True Wireless Stereo), adecuada para relajarse en casa o viajar al aire libre.</t>
+  </si>
+  <si>
+    <t>11108</t>
+  </si>
+  <si>
+    <t>9383</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>1.70%</t>
+  </si>
+  <si>
+    <t>604920287716838</t>
+  </si>
+  <si>
+    <t>El foco de techo LED de la marca MEGALUZ con una potencia de 18 vatios tiene una iluminación fría blanca de 6500K que se puede ajustar y es de tipo incrustado. El cuerpo del foco es ultra delgado y el tamaño del orificio de perforación se puede ajustar. Está fabricado con aluminio de alta calidad, lo que lo hace resistente a la corrosión y al óxido. Tiene un voltaje de trabajo entre 85 y 265 voltios y una frecuencia de 60 hercios. Es muy adecuado para salones, habitaciones, escaleras y pasillos.</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>3.67%</t>
+  </si>
+  <si>
+    <t>602298411512334</t>
+  </si>
+  <si>
+    <t>Musicord Altavoz Inalámbrico BT Portátil: ¡Sonido impactante, luces LED multicolores y 4 horas de autonomía! Compatible con TWS, FM, TF y USB – Imprescindible para fiestas y viajes</t>
+  </si>
+  <si>
+    <t>7257</t>
+  </si>
+  <si>
+    <t>5634</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>2.37%</t>
+  </si>
+  <si>
+    <t>604583719972405</t>
+  </si>
+  <si>
+    <t>Auriculares supraaurales envolventes inalámbricos Bluetooth 5.3, con diadema metálica, orejeras de piel de proteína, ligeros y plegables, para gaming, deportes y uso diario</t>
+  </si>
+  <si>
+    <t>23822</t>
+  </si>
+  <si>
+    <t>18657</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>0.48%</t>
+  </si>
+  <si>
+    <t>602329550025647</t>
+  </si>
+  <si>
+    <t>MEGALUZ Foco Emergencia Recargable 36W Alta Luminosidad 2500 Lúmenes, Bombilla Portátil Luz de Emergencia con Gancho Colgante, 3 Modos de Luz (Intensa/Normal/Intermitente), Batería Recargable Carga Micro USB, Lampara para Camping, Tianguis, Apagones Casa, Luz para Jardín Nocturno</t>
+  </si>
+  <si>
+    <t>1776</t>
+  </si>
+  <si>
+    <t>1332</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>2.53%</t>
+  </si>
+  <si>
+    <t>604756323999048</t>
+  </si>
+  <si>
+    <t>link bits Barra de Sonido para TV, 2x2" Altavoces + 2 Membranas de Graves, Sonido Claro ≥80dB, Bluetooth Inalámbrico, Conexiones AUX/USB, Diseño Compacto 76cm, Sonido Envolvente 3D para Cine en Casa, PC, Juegos y Fiestas</t>
+  </si>
+  <si>
+    <t>4517</t>
+  </si>
+  <si>
+    <t>3831</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>1.95%</t>
+  </si>
+  <si>
+    <t>605063145692961</t>
+  </si>
+  <si>
+    <t>Subwoofer Portátil Inalámbrico con Luces RGB, Sonido de Alta Potencia y Batería Duradera, TWS TF USB, Perfecto para Campamento Fiestas y Entretenimiento en Casa, Regalo Ideal para Amigos, Familia y Celebraciones Festivas</t>
+  </si>
+  <si>
+    <t>24324</t>
+  </si>
+  <si>
+    <t>20030</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>1.79%</t>
+  </si>
+  <si>
+    <t>604520050455943</t>
+  </si>
+  <si>
+    <t>La bocina portátil inalámbrica Linkbits cuenta con parlantes estéreo de dos altavoces de 3 pulgadas, luces de ambiente integradas y una batería recargable de gran capacidad que ofrece 3-4 horas de reproducción. Compatible con tarjeta TF, USB, radio FM y conexión inalámbrica, es ideal para cine en casa, fiestas al aire libre y campamentos.</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>937</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1.81%</t>
+  </si>
+  <si>
+    <t>602285526606889</t>
+  </si>
+  <si>
+    <t>Foco de bombilla LED de la marca TIANLAI. Tensión de trabajo: 127 voltios / Potencia: 48 vatios. Luz de color blanco frío de 6500K. El cuerpo de la bombilla está herméticamente sellado de forma integral, que es resistente al polvo y a los insectos, prolongando su vida útil. Tiene un conector enroscado estándar E27, lo que hace que la instalación sea muy fácil. Es muy adecuado para salones, dormitorios, estudios y garajes.</t>
+  </si>
+  <si>
+    <t>1391</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>3.45%</t>
+  </si>
+  <si>
+    <t>608676505077893</t>
+  </si>
+  <si>
+    <t>MEGALUZ Bombilla LED Recargable 120/180W con Larga Autonomía - Luz para Puestos Callejeros, Hogar, Exterior y Campamento, Iluminación de Emergencia</t>
+  </si>
+  <si>
+    <t>1760</t>
+  </si>
+  <si>
+    <t>1392</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>3.98%</t>
+  </si>
+  <si>
+    <t>604428782393798</t>
+  </si>
+  <si>
+    <t>Bocina Portátil , Parlante Portátil BT, Incorpora Luces De Ambiente. Posee La Función De Radio FM, La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Cargar A Través De USB. Tiene Forma De Cilindro, Pesa 198 Gramos Y Viene Con Un Cordón De Gancho, Lo Que La Hace Compacta Y Portátil. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
+  </si>
+  <si>
+    <t>1856</t>
+  </si>
+  <si>
+    <t>1437</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>1.24%</t>
+  </si>
+  <si>
+    <t>605335339264451</t>
+  </si>
+  <si>
+    <t>LINK BITS Bocina Portátil Inalámbrica 3 Pulgadas, Altavoz Bluetooth con Función TWS, Radio FM, Reproducción USB TF, Luces Ambientales, Batería Recargable 500mAh 5W, Mini Bocina Cuadrada Negra para Hogar Viaje Regalo</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1.33%</t>
+  </si>
+  <si>
+    <t>602355655355406</t>
+  </si>
+  <si>
+    <t>TIANLAI Ventilador de techo con luz LED RGB E27, 6 pulgadas, 40W, motor silencioso, fácil instalación, alto brillo 3800 lm, 127V. Ideal para dormitorios, salas y cocinas del hogar.</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>994</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>3.66%</t>
+  </si>
+  <si>
+    <t>602699789627377</t>
+  </si>
+  <si>
+    <t>Banda LED RGB de 5 Metros con Control Remoto - Puedes Recortar su Longitud, Conecta por USB - 12 Colores y 4 Modos de Parpadeo - Iluminación Creativa para Decorar el Fondo de la TV en Salón y Dormitorio</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3.03%</t>
+  </si>
+  <si>
+    <t>602944267191009</t>
+  </si>
+  <si>
+    <t>Lámpara bombilla de LED de 60 vatios de la marca MEGALUZ, con un voltaje de trabajo entre 85 y 265 voltios. Tiene un color de luz fría blanca con una temperatura de color de 6500K. Tiene una interfaz E27, lo que la hace muy fácil de instalar y es compatible con la mayoría de los soportes de lámparas. Con una luminosidad de 5700 lúmenes, es adecuada para salones, cocinas, dormitorios, despachos y garajes.</t>
+  </si>
+  <si>
+    <t>732</t>
+  </si>
+  <si>
+    <t>586</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>2.32%</t>
+  </si>
+  <si>
+    <t>603182235263112</t>
+  </si>
+  <si>
+    <t>Linkbits Bocina Portátil Parlantes BT Portátiles con Iluminación de Ambiente | 1 Hora de Duración, FM, TWS, TF/Micro SD | Ideal para Hogar, Fiestas y Viajes</t>
+  </si>
+  <si>
+    <t>2059</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>1.26%</t>
+  </si>
+  <si>
+    <t>604465289640816</t>
+  </si>
+  <si>
+    <t>Altavoz Mini Karaoke Portátil BT con Micrófono Inalámbrico, Función TWS, Radio FM, USB/TF, Batería de Larga Duración, Perfecto para Casa, Exterior y Regalos Especiales</t>
+  </si>
+  <si>
+    <t>796</t>
+  </si>
+  <si>
+    <t>706</t>
+  </si>
+  <si>
+    <t>2.14%</t>
+  </si>
+  <si>
+    <t>604543672787132</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Ventilador con luz LED, 25W, diámetro de 26cm. Incluye mando a distancia. Ajuste de tres velocidades de viento, función de regulación continua de tres temperaturas de color. Iluminación brillante, interfaz E27. Ajuste universal de 30°. Fácil de instalar. Adecuado para salón, dormitorio, estudio y otras escenas.</t>
+  </si>
+  <si>
+    <t>3.57%</t>
+  </si>
+  <si>
+    <t>604554141771212</t>
+  </si>
+  <si>
+    <t>Extractor de agua para garrafas de agua, compatible con carga USB, extractor de agua automático, práctico, con dos modos de toma de agua: manual y programado, ideal para dormitorios, salones, oficinas, uso al aire libre y otros escenarios.</t>
+  </si>
+  <si>
+    <t>5738</t>
+  </si>
+  <si>
+    <t>4591</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>604602510503489</t>
+  </si>
+  <si>
+    <t>LINK BITS Barra de Sonido Portátil Doble Parlante Sonido Envolvente Alta Calidad, TWS Radio FM USB TF AUX, Ideal Dormitorios Estudiantiles Escritorio, Regalo de Cumpleaños y Uso en Hogar</t>
+  </si>
+  <si>
+    <t>3739</t>
+  </si>
+  <si>
+    <t>3169</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>2.11%</t>
+  </si>
+  <si>
+    <t>604670424667185</t>
+  </si>
+  <si>
+    <t>Mascarillas Infantiles KF94 50 pcs, Cuatro Capas de Protección con Tejido de Fusión Filtrante, Patrones Divertidos, Piel Amigable y Transpirable</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>1.29%</t>
+  </si>
+  <si>
+    <t>604756323972961</t>
+  </si>
+  <si>
+    <t>Bocina Radio FM/Reproductor, Compatible con Tarjeta TF, USB, Bluetooth, Aplicable para celular, computadora, Ipad y consola.</t>
+  </si>
+  <si>
+    <t>6815</t>
+  </si>
+  <si>
+    <t>5796</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>604767011082762</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Tira de luces LED, luz azul/roja/verde de 127V, tira de luces LED impermeable y frío resistente de 32.8 pies / 10 metros, led 2835, con una vida útil de 50000 horas, larga duración. Se puede cortar libremente cada 10 cm. Adecuada para dormitorio, escalera, escritorio y otras escenas.</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>7.64%</t>
+  </si>
+  <si>
+    <t>604770232334794</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Tira de luces LED APP LED, tira de luces LED RGB de 5V regulable en múltiples colores, tira de luces impermeable de 16.4 pies / 5 metros, control doble por APP y mando a distancia, interfaz USB, led 5050, con una vida útil de 50000 horas, larga duración. Adecuada para fiestas, decoración doméstica, Navidad y otras escenas.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>604786338404390</t>
+  </si>
+  <si>
+    <t>Linkbits Altavoz de 8 pulgadas, compatible con Bluetooth/USB/TF, respuesta en frecuencia de 100Hz - 20kHz, incluye micrófono cableado integrado, batería de litio incorporada, alimentación flexible AC/DC, autonomía de 1-2 horas, ideal para lugares de entretenimiento, bares de música y otros entornos.</t>
+  </si>
+  <si>
+    <t>2149</t>
+  </si>
+  <si>
+    <t>1633</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1.68%</t>
+  </si>
+  <si>
+    <t>604812913531275</t>
+  </si>
+  <si>
+    <t>Linkbits，Bocina portátil，Parlantes BT portátiles， tiene luces de ambiente incorporadas. Tiene una duración de 2 horas, cuenta con radio FM, función TWS (True Wireless Stereo), y soporta tarjetas TF y carga a través de USB. Ya sea para relajarse en casa, celebrar fiestas o viajar, es una opción ideal.</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2.29%</t>
+  </si>
+  <si>
+    <t>604848883888106</t>
+  </si>
+  <si>
+    <t>TIANLAI Ventilador Lámpara Techo Empotrada LED, Conector E27 Fácil de Instalar, Incluye Control Remoto, Brillo Ajustable, Temperatura de Luz 3000K-6500K, 3 Colores de Luz, 3 Velocidades de Viento, 30W, Voltaje de Trabajo 85-265V, Ideal para Dormitorio, Comedor y Sala de Estar</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>604886196420214</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Tira de luces LED, tira de luces LED RGB de 12V regulable en múltiples colores, tira de luces impermeable de 16.4 pies / 5 metros. Incluye mando a distancia y adaptador de corriente, led 5050, con una vida útil de 50000 horas, larga duración. Adecuada para fiestas, decoración doméstica, Navidad y otras escenas.</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1.90%</t>
+  </si>
+  <si>
+    <t>604886464870578</t>
+  </si>
+  <si>
+    <t>Lámpara LED blanca TIANLAI de 6500K, con luz suave, con conector en rosca E27 estándar, es fácil de instalar, tiene una potencia de 10 vatios, es energéticamente eficiente y tiene una hermética sellación, tiene una larga duración útil. Es adecuada para la iluminación interior y se puede utilizar en hogares y oficinas.</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>604938809759478</t>
+  </si>
+  <si>
+    <t>Bocina Portátil, Parlantes BT Portátiles, de 4 Pulgadas, Altavoz Inalámbrico, con Iluminación LED, Sonido Estéreo, Compatible con USB/ Tarjeta TF/ Micrófono, Soporta Radio FM, Posee Función de Voz Mágica y Diseño con Asa, Ideal para Viajar, Trabajar y Entretenerte</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>1.06%</t>
+  </si>
+  <si>
+    <t>604973169502870</t>
+  </si>
+  <si>
+    <t>Linkbits Bocina Portátil De BT, Con Un Altavoz De 8 Pulgadas Y Luces De Ambiente Incorporadas. Tiene Una Duración De 3 Horas, Incluye Un Micrófono Limitado, Es Compatible Con La Radio FM, La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Cargar A Través De USB. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>605000331828170</t>
+  </si>
+  <si>
+    <t>Link bits HD005 Antena UHF para Exteriores, Antena de TV Digital HD con 10 Metros de Cable, Recepción 470-862MHz, 9-7dB de Ganancia, Antena para Canales Abiertos y HD, Resistente al Agua y Viento, Fácil Instalación</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>5.00%</t>
+  </si>
+  <si>
+    <t>605023417259114</t>
+  </si>
+  <si>
+    <t>Link Bits Ventilador de piso de 16 pulgadas, 2 unidades, 3 velocidades, motor silencioso, flujo de aire fuerte, altura ajustable, oscilación amplia, ventilador eléctrico para el hogar, ideal para sala, recámara y oficina</t>
+  </si>
+  <si>
+    <t>400.00%</t>
+  </si>
+  <si>
+    <t>605049405188789</t>
+  </si>
+  <si>
+    <t>Megaluz，Ventilador De Techo Con Lámpara LED， LV34W04 ， potente viento, 34 Vatios, Base De Enchufe E27, Fácil De Instalar, Luz Fría Blanca De 2720 Lm, Con Tres Modos, Aspas Externas, Motor Silencioso (Controlado Por Interruptor),Una Excelente Opción Para El Hogar En Veran</t>
+  </si>
+  <si>
+    <t>605115708707647</t>
+  </si>
+  <si>
+    <t>Linkbits Altavoz Bluetooth Portátil - Luces LED RGB 360°, Bajos Potentes de 24W, Estéreo TWS y Asa para Exterior/Fiestas</t>
+  </si>
+  <si>
+    <t>768</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2.21%</t>
+  </si>
+  <si>
+    <t>605131009575368</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Cabeza de farola, 100W, múltiples ledes 2835/5000lm, vida útil larga de 50000h, amplio rango de iluminación, buena impermeabilidad y disipación de calor, se instala con varios estilos de postes, voltaje de trabajo 127V, ideal para canchas de deporte, carreteras, túneles y otros escenarios.</t>
+  </si>
+  <si>
+    <t>605165369319245</t>
+  </si>
+  <si>
+    <t>TIANLAI Ventilador de Techo de 22W con Luz, 1000LM 6500K Base E27, 5 Aspas 1 Velocidad, 16.5"×6.7", CRI&gt;80, Control por Interruptor, Ahorro de Energía para Dormitorio y Sala de Estar</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>0.72%</t>
+  </si>
+  <si>
+    <t>605168640823168</t>
+  </si>
+  <si>
+    <t>Linkbits Altavoz Bluetooth Portátil con Stereo Inalámbrico TWS Impermeable y a Prueba de Polvo IP65 Altavoz de Graves de Rango Completo de 52mm con Doble Unidad Ligero de 215g para Camping Senderismo y Fiestas al Aire Libre</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>1.91%</t>
+  </si>
+  <si>
+    <t>605278162545829</t>
+  </si>
+  <si>
+    <t>Link bits Portable Bluetooth Speaker - 800W Peak Power, 50W Full-Range Audio with Dual Bass System &amp; Deep Bass Membranes, Powerful &amp; Distortion-Free Sound, IP65 Waterproof Dustproof, TWS Support &amp; 6H Battery for Outdoor/Party</t>
   </si>
   <si>
     <t>737</t>
   </si>
   <si>
-    <t>1.01%</t>
-  </si>
-  <si>
-    <t>602978090117530</t>
-  </si>
-  <si>
-    <t>Bocina inalámbrica de la marca LINK BITS. Tiene un altavoz grande de 8 pulgadas, un sonido estéreo, una interfaz USB. Tiene una batería recargable interna de 1200 mAh. Cuenta con funciones de control de altavoz y microfono. Tiene luces LED. Apoya tarjetas TF, la recepción de radio FM y la interconexión inalámbrica TWS (True Wireless Stereo). Es una bocina adecuada para fiestas en casa, karaoke y uso al aire libre.</t>
-  </si>
-  <si>
-    <t>6131</t>
-  </si>
-  <si>
-    <t>4636</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2.15%</t>
-  </si>
-  <si>
-    <t>604444133541993</t>
-  </si>
-  <si>
-    <t>Soporte Articulado de Pared para TV LCD LED Smart de 14 a 55 Pulgadas, Brazo Telescópico 3 Brazos Extensible y Retráctil, Giro Horizontal ±90°, Inclinación ±15°, Carga Hasta 25kg, Compatible VESA 75x75 hasta 400x400, Para Pared de Ladrillo, Madera y Hormigón</t>
-  </si>
-  <si>
-    <t>6321</t>
-  </si>
-  <si>
-    <t>5521</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>0.85%</t>
-  </si>
-  <si>
-    <t>608113864355784</t>
-  </si>
-  <si>
-    <t>Audífonos diadema over-ear Bluetooth 5.4 con micrófono HD y baja latencia, plegables ergonómicos para estudiar, ver series y jugar en celular, laptop y consola, conexión estable sin cortes</t>
-  </si>
-  <si>
-    <t>10713</t>
-  </si>
-  <si>
-    <t>7725</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>2.59%</t>
-  </si>
-  <si>
-    <t>602329550025647</t>
-  </si>
-  <si>
-    <t>MEGALUZ - Lámpara de emergencia portátil móvil de 36 vatios, con un gancho incorporado. Tiene luz blanca de 6500K, y se puede ajustar en múltiples modos de iluminación. Es una lámpara colgante con un puerto USB y una lámpara de carga USB. Es adecuada como lámpara de emergencia LED para el hogar, lámpara de emergencia de bombilla para acampar al aire libre, o para iluminar jardines en mercados nocturnos. Te brinda una experiencia de iluminación súper brillante.</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>2.96%</t>
-  </si>
-  <si>
-    <t>602298411512334</t>
-  </si>
-  <si>
-    <t>Musicord Altavoz Inalámbrico BT Portátil: ¡Sonido impactante, luces LED multicolores y 4 horas de autonomía! Compatible con TWS, FM, TF y USB – Imprescindible para fiestas y viajes</t>
-  </si>
-  <si>
-    <t>4619</t>
-  </si>
-  <si>
-    <t>3620</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>2.40%</t>
-  </si>
-  <si>
-    <t>604920287716838</t>
-  </si>
-  <si>
-    <t>El foco de techo LED de la marca MEGALUZ con una potencia de 18 vatios tiene una iluminación fría blanca de 6500K que se puede ajustar y es de tipo incrustado. El cuerpo del foco es ultra delgado y el tamaño del orificio de perforación se puede ajustar. Está fabricado con aluminio de alta calidad, lo que lo hace resistente a la corrosión y al óxido. Tiene un voltaje de trabajo entre 85 y 265 voltios y una frecuencia de 60 hercios. Es muy adecuado para salones, habitaciones, escaleras y pasillos.</t>
-  </si>
-  <si>
-    <t>1174</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>3.15%</t>
-  </si>
-  <si>
-    <t>604756323999048</t>
-  </si>
-  <si>
-    <t>link bits Barra de Sonido para TV, 2x2" Altavoces + 2 Membranas de Graves, Sonido Claro ≥80dB, Bluetooth Inalámbrico, Conexiones AUX/USB, Diseño Compacto 76cm, Sonido Envolvente 3D para Cine en Casa, PC, Juegos y Fiestas</t>
-  </si>
-  <si>
-    <t>3030</t>
-  </si>
-  <si>
-    <t>2564</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>1.82%</t>
-  </si>
-  <si>
-    <t>604583719972405</t>
-  </si>
-  <si>
-    <t>Auriculares supraaurales envolventes inalámbricos Bluetooth 5.3, con diadema metálica, orejeras de piel de proteína, ligeros y plegables, para gaming, deportes y uso diario</t>
-  </si>
-  <si>
-    <t>16793</t>
-  </si>
-  <si>
-    <t>13351</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>0.46%</t>
-  </si>
-  <si>
-    <t>605063145692961</t>
-  </si>
-  <si>
-    <t>Subwoofer Portátil Inalámbrico con Luces RGB, Sonido de Alta Potencia y Batería Duradera, TWS TF USB, Perfecto para Campamento Fiestas y Entretenimiento en Casa</t>
-  </si>
-  <si>
-    <t>15343</t>
-  </si>
-  <si>
-    <t>12744</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>1.77%</t>
-  </si>
-  <si>
-    <t>604835730556993</t>
-  </si>
-  <si>
-    <t>Bocina portátil Inalámbrico, de 3 pulgadas, tamaño de bolsillo, 170 g, con asa, compatible con TF, USB y Micro SD, con radio FM y función TWS (True Wireless Stereo), adecuada para relajarse en casa o viajar al aire libre.</t>
-  </si>
-  <si>
-    <t>7388</t>
-  </si>
-  <si>
-    <t>6271</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>1.68%</t>
-  </si>
-  <si>
-    <t>602285526606889</t>
-  </si>
-  <si>
-    <t>Foco de bombilla LED de la marca TIANLAI. Tensión de trabajo: 127 voltios / Potencia: 48 vatios. Luz de color blanco frío de 6500K. El cuerpo de la bombilla está herméticamente sellado de forma integral, que es resistente al polvo y a los insectos, prolongando su vida útil. Tiene un conector enroscado estándar E27, lo que hace que la instalación sea muy fácil. Es muy adecuado para salones, dormitorios, estudios y garajes.</t>
-  </si>
-  <si>
-    <t>942</t>
-  </si>
-  <si>
-    <t>695</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>3.08%</t>
-  </si>
-  <si>
-    <t>608676505077893</t>
-  </si>
-  <si>
-    <t>MEGALUZ Bombilla LED Recargable 120/180W con Larga Autonomía - Luz para Puestos Callejeros, Hogar, Exterior y Campamento, Iluminación de Emergencia</t>
-  </si>
-  <si>
-    <t>1318</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>3.64%</t>
-  </si>
-  <si>
-    <t>602355655355406</t>
-  </si>
-  <si>
-    <t>TIANLAI Ventilador de techo con luz LED RGB E27, 6 pulgadas, 40W, motor silencioso, fácil instalación, alto brillo 3800 lm, 127V. Ideal para dormitorios, salas y cocinas del hogar.</t>
-  </si>
-  <si>
-    <t>827</t>
-  </si>
-  <si>
-    <t>688</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>3.99%</t>
-  </si>
-  <si>
-    <t>602699789627377</t>
-  </si>
-  <si>
-    <t>Banda LED RGB de 5 Metros con Control Remoto - Puedes Recortar su Longitud, Conecta por USB - 12 Colores y 4 Modos de Parpadeo - Iluminación Creativa para Decorar el Fondo de la TV en Salón y Dormitorio</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>5.56%</t>
-  </si>
-  <si>
-    <t>602944267191009</t>
-  </si>
-  <si>
-    <t>Lámpara bombilla de LED de 60 vatios de la marca MEGALUZ, con un voltaje de trabajo entre 85 y 265 voltios. Tiene un color de luz fría blanca con una temperatura de color de 6500K. Tiene una interfaz E27, lo que la hace muy fácil de instalar y es compatible con la mayoría de los soportes de lámparas. Con una luminosidad de 5700 lúmenes, es adecuada para salones, cocinas, dormitorios, despachos y garajes.</t>
-  </si>
-  <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>2.91%</t>
-  </si>
-  <si>
-    <t>603182235263112</t>
-  </si>
-  <si>
-    <t>Linkbits Bocina Portátil Parlantes BT Portátiles con Iluminación de Ambiente | 1 Hora de Duración, FM, TWS, TF/Micro SD | Ideal para Hogar, Fiestas y Viajes</t>
-  </si>
-  <si>
-    <t>1424</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1.33%</t>
-  </si>
-  <si>
-    <t>604428782393798</t>
-  </si>
-  <si>
-    <t>Bocina Portátil , Parlante Portátil BT, Incorpora Luces De Ambiente. Posee La Función De Radio FM, La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Cargar A Través De USB. Tiene Forma De Cilindro, Pesa 198 Gramos Y Viene Con Un Cordón De Gancho, Lo Que La Hace Compacta Y Portátil. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
-  </si>
-  <si>
-    <t>1341</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>1.27%</t>
-  </si>
-  <si>
-    <t>604465289640816</t>
-  </si>
-  <si>
-    <t>Altavoz Mini Karaoke Portátil BT con Micrófono Inalámbrico, Función TWS, Radio FM, USB/TF, Batería de Larga Duración, Perfecto para Casa, Exterior y Regalos Especiales</t>
-  </si>
-  <si>
-    <t>540</t>
-  </si>
-  <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>2.41%</t>
-  </si>
-  <si>
-    <t>604520050455943</t>
-  </si>
-  <si>
-    <t>La bocina portátil inalámbrica Linkbits cuenta con parlantes estéreo de dos altavoces de 3 pulgadas, luces de ambiente integradas y una batería recargable de gran capacidad que ofrece 3-4 horas de reproducción. Compatible con tarjeta TF, USB, radio FM y conexión inalámbrica, es ideal para cine en casa, fiestas al aire libre y campamentos.</t>
-  </si>
-  <si>
-    <t>772</t>
-  </si>
-  <si>
-    <t>631</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>2.07%</t>
-  </si>
-  <si>
-    <t>604543672787132</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Ventilador con luz LED, 25W, diámetro de 26cm. Incluye mando a distancia. Ajuste de tres velocidades de viento, función de regulación continua de tres temperaturas de color. Iluminación brillante, interfaz E27. Ajuste universal de 30°. Fácil de instalar. Adecuado para salón, dormitorio, estudio y otras escenas.</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2.63%</t>
-  </si>
-  <si>
-    <t>604554141771212</t>
-  </si>
-  <si>
-    <t>Extractor de agua para garrafas de agua, compatible con carga USB, extractor de agua automático, práctico, con dos modos de toma de agua: manual y programado, ideal para dormitorios, salones, oficinas, uso al aire libre y otros escenarios.</t>
-  </si>
-  <si>
-    <t>3890</t>
-  </si>
-  <si>
-    <t>3127</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>2.06%</t>
-  </si>
-  <si>
-    <t>604602510503489</t>
-  </si>
-  <si>
-    <t>LINK BITS Barra de Sonido Portátil Doble Parlante Sonido Envolvente Alta Calidad, TWS Radio FM USB TF AUX, Ideal Dormitorios Estudiantiles Escritorio, Regalo de Cumpleaños y Uso en Hogar</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2149</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>1.80%</t>
-  </si>
-  <si>
-    <t>604670424667185</t>
-  </si>
-  <si>
-    <t>Mascarillas Infantiles KF94 50 pcs, Cuatro Capas de Protección con Tejido de Fusión Filtrante, Patrones Divertidos, Piel Amigable y Transpirable</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>0.93%</t>
-  </si>
-  <si>
-    <t>604756323972961</t>
-  </si>
-  <si>
-    <t>Bocina Radio FM/Reproductor, Compatible con Tarjeta TF, USB, Bluetooth, Aplicable para celular, computadora, Ipad y consola.</t>
-  </si>
-  <si>
-    <t>4353</t>
-  </si>
-  <si>
-    <t>3723</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>1.93%</t>
-  </si>
-  <si>
-    <t>604767011082762</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Tira de luces LED, luz azul/roja/verde de 127V, tira de luces LED impermeable y frío resistente de 32.8 pies / 10 metros, led 2835, con una vida útil de 50000 horas, larga duración. Se puede cortar libremente cada 10 cm. Adecuada para dormitorio, escalera, escritorio y otras escenas.</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>9.57%</t>
-  </si>
-  <si>
-    <t>604770232334794</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Tira de luces LED APP LED, tira de luces LED RGB de 5V regulable en múltiples colores, tira de luces impermeable de 16.4 pies / 5 metros, control doble por APP y mando a distancia, interfaz USB, led 5050, con una vida útil de 50000 horas, larga duración. Adecuada para fiestas, decoración doméstica, Navidad y otras escenas.</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>604786338404390</t>
-  </si>
-  <si>
-    <t>Linkbits Altavoz de 8 pulgadas, compatible con Bluetooth/USB/TF, respuesta en frecuencia de 100Hz - 20kHz, incluye micrófono cableado integrado, batería de litio incorporada, alimentación flexible AC/DC, autonomía de 1-2 horas, ideal para lugares de entretenimiento, bares de música y otros entornos.</t>
-  </si>
-  <si>
-    <t>1539</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>1.17%</t>
-  </si>
-  <si>
-    <t>604812913531275</t>
-  </si>
-  <si>
-    <t>Linkbits，Bocina portátil，Parlantes BT portátiles， tiene luces de ambiente incorporadas. Tiene una duración de 2 horas, cuenta con radio FM, función TWS (True Wireless Stereo), y soporta tarjetas TF y carga a través de USB. Ya sea para relajarse en casa, celebrar fiestas o viajar, es una opción ideal.</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2.82%</t>
-  </si>
-  <si>
-    <t>604848883888106</t>
-  </si>
-  <si>
-    <t>TIANLAI Ventilador Lámpara Techo Empotrada LED, Conector E27 Fácil de Instalar, Incluye Control Remoto, Brillo Ajustable, Temperatura de Luz 3000K-6500K, 3 Colores de Luz, 3 Velocidades de Viento, 30W, Voltaje de Trabajo 85-265V, Ideal para Dormitorio, Comedor y Sala de Estar</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>604886196420214</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Tira de luces LED, tira de luces LED RGB de 12V regulable en múltiples colores, tira de luces impermeable de 16.4 pies / 5 metros. Incluye mando a distancia y adaptador de corriente, led 5050, con una vida útil de 50000 horas, larga duración. Adecuada para fiestas, decoración doméstica, Navidad y otras escenas.</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>1.37%</t>
-  </si>
-  <si>
-    <t>604886464870578</t>
-  </si>
-  <si>
-    <t>Lámpara LED blanca TIANLAI de 6500K, con luz suave, con conector en rosca E27 estándar, es fácil de instalar, tiene una potencia de 10 vatios, es energéticamente eficiente y tiene una hermética sellación, tiene una larga duración útil. Es adecuada para la iluminación interior y se puede utilizar en hogares y oficinas.</t>
-  </si>
-  <si>
-    <t>604938809759478</t>
-  </si>
-  <si>
-    <t>Bocina Portátil, Parlantes BT Portátiles, de 4 Pulgadas, Altavoz Inalámbrico, con Iluminación LED, Sonido Estéreo, Compatible con USB/ Tarjeta TF/ Micrófono, Soporta Radio FM, Posee Función de Voz Mágica y Diseño con Asa, Ideal para Viajar, Trabajar y Entretenerte</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>1.69%</t>
-  </si>
-  <si>
-    <t>604973169502870</t>
-  </si>
-  <si>
-    <t>Linkbits Bocina Portátil De BT, Con Un Altavoz De 8 Pulgadas Y Luces De Ambiente Incorporadas. Tiene Una Duración De 3 Horas, Incluye Un Micrófono Limitado, Es Compatible Con La Radio FM, La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Cargar A Través De USB. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
-  </si>
-  <si>
-    <t>605000331828170</t>
-  </si>
-  <si>
-    <t>Link bits HD005 Antena UHF para Exteriores, Antena de TV Digital HD con 10 Metros de Cable, Recepción 470-862MHz, 9-7dB de Ganancia, Antena para Canales Abiertos y HD, Resistente al Agua y Viento, Fácil Instalación</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>4.00%</t>
-  </si>
-  <si>
-    <t>605023417259114</t>
-  </si>
-  <si>
-    <t>Link Bits Ventilador de piso de 16 pulgadas, 2 unidades, 3 velocidades, motor silencioso, flujo de aire fuerte, altura ajustable, oscilación amplia, ventilador eléctrico para el hogar, ideal para sala, recámara y oficina</t>
-  </si>
-  <si>
-    <t>605049405188789</t>
-  </si>
-  <si>
-    <t>Megaluz，Ventilador De Techo Con Lámpara LED， LV34W04 ， potente viento, 34 Vatios, Base De Enchufe E27, Fácil De Instalar, Luz Fría Blanca De 2720 Lm, Con Tres Modos, Aspas Externas, Motor Silencioso (Controlado Por Interruptor),Una Excelente Opción Para El Hogar En Veran</t>
-  </si>
-  <si>
-    <t>605115708707647</t>
-  </si>
-  <si>
-    <t>Linkbits Altavoz Bluetooth Portátil - Luces LED RGB 360°, Bajos Potentes de 24W, Estéreo TWS y Asa para Exterior/Fiestas</t>
-  </si>
-  <si>
-    <t>507</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2.37%</t>
-  </si>
-  <si>
-    <t>605131009575368</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Cabeza de farola, 100W, múltiples ledes 2835/5000lm, vida útil larga de 50000h, amplio rango de iluminación, buena impermeabilidad y disipación de calor, se instala con varios estilos de postes, voltaje de trabajo 127V, ideal para canchas de deporte, carreteras, túneles y otros escenarios.</t>
-  </si>
-  <si>
-    <t>605165369319245</t>
-  </si>
-  <si>
-    <t>Ventilador de Techo LED TIANLAI con 5 Aspas, Control Remoto, 3 Colores Luz, 3 Velocidades, Temporizador, Fácil Instalación, E27 para Baño Cocina Dormitorio Salón</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>605168640823168</t>
-  </si>
-  <si>
-    <t>Linkbits Altavoz Bluetooth Portátil con Stereo Inalámbrico TWS Impermeable y a Prueba de Polvo IP65 Altavoz de Graves de Rango Completo de 52mm con Doble Unidad Ligero de 215g para Camping Senderismo y Fiestas al Aire Libre</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>2.30%</t>
-  </si>
-  <si>
-    <t>605278162545829</t>
-  </si>
-  <si>
-    <t>Link bits Portable Bluetooth Speaker - 800W Peak Power, 50W Full-Range Audio with Dual Bass System &amp; Deep Bass Membranes, Powerful &amp; Distortion-Free Sound, IP65 Waterproof Dustproof, TWS Support &amp; 6H Battery for Outdoor/Party</t>
-  </si>
-  <si>
-    <t>467</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>2.36%</t>
-  </si>
-  <si>
-    <t>605335339264451</t>
-  </si>
-  <si>
-    <t>LINK BITS Bocina Portátil Inalámbrica 3 Pulgadas, Altavoz Bluetooth con Función TWS, Radio FM, Reproducción USB TF, Luces Ambientales, Batería Recargable 500mAh 5W, Mini Bocina Cuadrada Negra para Hogar Viaje Regalo</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>627</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1.35%</t>
+    <t>588</t>
+  </si>
+  <si>
+    <t>2.99%</t>
   </si>
   <si>
     <t>605368088400485</t>
@@ -743,31 +755,34 @@
     <t>Bocina Portátil Bluetooth de 3 Pulgadas con Radio FM, USB TF TWS, Sonido Estéreo 5W, Bocina Recargable para Hogar Exterior Viaje Fiesta Camping</t>
   </si>
   <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>972</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2.14%</t>
+    <t>1726</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>2.09%</t>
   </si>
   <si>
     <t>608491821450328</t>
   </si>
   <si>
-    <t>Panel LED Circular Empotrable S61W 12W/18W 3 Tonos de Luz, Luminaria para Hogar y Local Comercial, Voltaje Amplio 85-265V Iluminación Interior Económica</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>2.69%</t>
+    <t>Panel LED circular ultra delgado empotrable tipo downlight, lámpara de techo negra 3 tonos de luz voltaje amplio, iluminación interior para dormitorios, pasillos, tiendas y oficinas</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2.92%</t>
   </si>
 </sst>
 </file>
@@ -1172,10 +1187,10 @@
         <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -1183,25 +1198,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -1209,25 +1224,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1235,25 +1250,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -1261,25 +1276,25 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
@@ -1287,25 +1302,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -1313,25 +1328,25 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
@@ -1339,25 +1354,25 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
@@ -1365,25 +1380,25 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21">
@@ -1391,25 +1406,25 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="H21" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
@@ -1417,25 +1432,25 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
@@ -1443,25 +1458,25 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24">
@@ -1469,25 +1484,25 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -1495,25 +1510,25 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="G25" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
@@ -1521,22 +1536,22 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="H26" t="s">
         <v>162</v>
@@ -1562,10 +1577,10 @@
         <v>167</v>
       </c>
       <c r="G27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -1582,16 +1597,16 @@
         <v>171</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29">
@@ -1599,13 +1614,13 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E29" t="s">
         <v>177</v>
@@ -1614,7 +1629,7 @@
         <v>178</v>
       </c>
       <c r="G29" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="H29" t="s">
         <v>179</v>
@@ -1637,13 +1652,13 @@
         <v>183</v>
       </c>
       <c r="F30" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31">
@@ -1651,25 +1666,25 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F31" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="G31" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="H31" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32">
@@ -1677,25 +1692,25 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G32" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H32" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33">
@@ -1703,25 +1718,25 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="F33" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G33" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34">
@@ -1729,25 +1744,25 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C34" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>206</v>
       </c>
       <c r="F34" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="H34" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35">
@@ -1755,25 +1770,25 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="G35" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="H35" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36">
@@ -1781,25 +1796,25 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D36" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G36" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H36" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37">
@@ -1807,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38">
@@ -1833,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C38" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="E38" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="F38" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="G38" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39">
@@ -1859,25 +1874,25 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D39" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E39" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F39" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="G39" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="H39" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
@@ -1885,25 +1900,25 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="G40" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41">
@@ -1911,25 +1926,25 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D41" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="E41" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="F41" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G41" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H41" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42">
@@ -1937,25 +1952,25 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C42" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D42" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E42" t="s">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="G42" t="s">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="H42" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43">
@@ -1963,25 +1978,25 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D43" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E43" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="G43" t="s">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="H43" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44">
@@ -1989,25 +2004,25 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E44" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F44" t="s">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="G44" t="s">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45">
@@ -2015,25 +2030,25 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D45" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E45" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F45" t="s">
-        <v>245</v>
+        <v>184</v>
       </c>
       <c r="G45" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H45" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46">
@@ -2041,25 +2056,25 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C46" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D46" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F46" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="G46" t="s">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="H46" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
